--- a/public/content-import-templates/05_lesson_explanations_template.xlsx
+++ b/public/content-import-templates/05_lesson_explanations_template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
   <si>
     <t>05 — نموذج شروحات الدرس</t>
   </si>
@@ -32,12 +32,24 @@
     <t>— الأعمدة —</t>
   </si>
   <si>
+    <t>subject_code *</t>
+  </si>
+  <si>
+    <t>ملاحظة: إلزامي — يحدد المادة التي ينتمي إليها lesson_code — مثال: phys-g10-aden</t>
+  </si>
+  <si>
     <t>lesson_code *</t>
   </si>
   <si>
     <t>مثال: phys-g10-u1-l1</t>
   </si>
   <si>
+    <t>explanation_code *</t>
+  </si>
+  <si>
+    <t>ملاحظة: هوية ثابتة للشرح — لا تغيّرها بين الدفعات — مثال: EXP-PHYS-G10-U1-L1-01</t>
+  </si>
+  <si>
     <t>title *</t>
   </si>
   <si>
@@ -86,7 +98,13 @@
     <t>يمكن إضافة أكثر من شرح لنفس lesson_code.</t>
   </si>
   <si>
+    <t>phys-g10-aden</t>
+  </si>
+  <si>
     <t>phys-g10-u1-l1</t>
+  </si>
+  <si>
+    <t>EXP-PHYS-G10-U1-L1-01</t>
   </si>
   <si>
     <t>شرح النظام الدولي للوحدات</t>
@@ -493,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -566,57 +584,73 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="B13" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="B12" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -627,15 +661,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="21" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -651,26 +687,38 @@
       <c r="E1" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>27</v>
+      <c r="G2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1"/>
+  <autoFilter ref="A1:G1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/public/content-import-templates/05_lesson_explanations_template.xlsx
+++ b/public/content-import-templates/05_lesson_explanations_template.xlsx
@@ -5,14 +5,15 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="تعليمات" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="الشروحات" state="visible" r:id="rId5"/>
+    <sheet sheetId="2" name="مرجع الأكواد" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="الشروحات" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="85">
   <si>
     <t>05 — نموذج شروحات الدرس</t>
   </si>
@@ -35,19 +36,19 @@
     <t>subject_code *</t>
   </si>
   <si>
-    <t>ملاحظة: إلزامي — يحدد المادة التي ينتمي إليها lesson_code — مثال: phys-g10-aden</t>
+    <t>ملاحظة: إلزامي — يحدد المادة التي ينتمي إليها lesson_code — مثال: sub-g10-aden-001</t>
   </si>
   <si>
     <t>lesson_code *</t>
   </si>
   <si>
-    <t>مثال: phys-g10-u1-l1</t>
+    <t>مثال: lesson-g10-aden-001-001</t>
   </si>
   <si>
     <t>explanation_code *</t>
   </si>
   <si>
-    <t>ملاحظة: هوية ثابتة للشرح — لا تغيّرها بين الدفعات — مثال: EXP-PHYS-G10-U1-L1-01</t>
+    <t>ملاحظة: هوية ثابتة للشرح — لا تغيّرها بين الدفعات — مثال: exp-g10-aden-001-001-01</t>
   </si>
   <si>
     <t>title *</t>
@@ -83,7 +84,10 @@
     <t>هذه النماذج لتجهيز المحتوى قبل الاستيراد — لا تستورد بيانات فعلية من هنا تلقائياً.</t>
   </si>
   <si>
-    <t>استخدم أكواداً نصية ثابتة (snake_case أو kebab-case) — لا تستخدم UUID.</t>
+    <t>الأكواد يملكها النظام (TCS-1): نزّل القالب الجاهز من «مركز الاستيراد» ولا تكتب كوداً يدوياً.</t>
+  </si>
+  <si>
+    <t>راجع ورقة «مرجع الأكواد» داخل الملف قبل التعبئة — لا تستخدم UUID ولا حروفاً عربية في الأكواد.</t>
   </si>
   <si>
     <t>لا تضع مفاتيح API أو روابط signed أو أسرار في الملفات.</t>
@@ -98,13 +102,163 @@
     <t>يمكن إضافة أكثر من شرح لنفس lesson_code.</t>
   </si>
   <si>
-    <t>phys-g10-aden</t>
-  </si>
-  <si>
-    <t>phys-g10-u1-l1</t>
-  </si>
-  <si>
-    <t>EXP-PHYS-G10-U1-L1-01</t>
+    <t>مرجع الأكواد الرسمي — TCS-1</t>
+  </si>
+  <si>
+    <t>— صيغ الأكواد —</t>
+  </si>
+  <si>
+    <t>مادة</t>
+  </si>
+  <si>
+    <t>sub-{gradeShort}-{trackCode}-{subjectNo:003}</t>
+  </si>
+  <si>
+    <t>مثال: sub-g10-aden-003</t>
+  </si>
+  <si>
+    <t>مجموعة مواد</t>
+  </si>
+  <si>
+    <t>grp-{gradeShort}-{trackCode}-{groupNo:02}</t>
+  </si>
+  <si>
+    <t>مثال: grp-g10-aden-01</t>
+  </si>
+  <si>
+    <t>وحدة</t>
+  </si>
+  <si>
+    <t>unit-{gradeShort}-{trackCode}-{subjectNo:003}-{unitNo:02}</t>
+  </si>
+  <si>
+    <t>مثال: unit-g10-aden-003-02</t>
+  </si>
+  <si>
+    <t>درس</t>
+  </si>
+  <si>
+    <t>lesson-{gradeShort}-{trackCode}-{subjectNo:003}-{lessonNo:003}</t>
+  </si>
+  <si>
+    <t>مثال: lesson-g10-aden-003-004</t>
+  </si>
+  <si>
+    <t>شرح</t>
+  </si>
+  <si>
+    <t>exp-{gradeShort}-{trackCode}-{subjectNo:003}-{lessonNo:003}-{seq:02}</t>
+  </si>
+  <si>
+    <t>مثال: exp-g10-aden-003-004-01</t>
+  </si>
+  <si>
+    <t>مورد</t>
+  </si>
+  <si>
+    <t>res-{gradeShort}-{trackCode}-{subjectNo:003}-{lessonNo:003}-{seq:02}</t>
+  </si>
+  <si>
+    <t>مثال: res-g10-aden-003-004-01</t>
+  </si>
+  <si>
+    <t>تقييم</t>
+  </si>
+  <si>
+    <t>asm-{gradeShort}-{trackCode}-{subjectNo:003}-{lessonNo:003}-{seq:02}</t>
+  </si>
+  <si>
+    <t>مثال: asm-g10-aden-003-004-01</t>
+  </si>
+  <si>
+    <t>سؤال</t>
+  </si>
+  <si>
+    <t>q-{gradeShort}-{trackCode}-{subjectNo:003}-{questionNo:05}</t>
+  </si>
+  <si>
+    <t>مثال: q-g10-aden-003-00007</t>
+  </si>
+  <si>
+    <t>— القواعد —</t>
+  </si>
+  <si>
+    <t>نظام الأكواد الرسمي: TCS-1 — الأكواد يولّدها النظام ولا ينشئها المشغّل يدوياً.</t>
+  </si>
+  <si>
+    <t>الكود مستقل عن الاسم العربي: تغيير الاسم لا يغيّر الكود أبداً.</t>
+  </si>
+  <si>
+    <t>كود الدرس لا يحتوي على كود الوحدة، لذلك يمكن نقل الدرس بين الوحدات دون تغيير هويته.</t>
+  </si>
+  <si>
+    <t>كود السؤال لا يحتوي على الدرس، لأنه هوية ثابتة عبر المراجعات والاستهداف.</t>
+  </si>
+  <si>
+    <t>الصف والمسار داخل الكود مأخوذان من البيانات المرجعية الرسمية فقط.</t>
+  </si>
+  <si>
+    <t>أي كود سبق تخصيصه لا يُعاد استخدامه لكيان آخر حتى بعد الحذف.</t>
+  </si>
+  <si>
+    <t>— الصفوف المعتمدة —</t>
+  </si>
+  <si>
+    <t>g10</t>
+  </si>
+  <si>
+    <t>grade-10</t>
+  </si>
+  <si>
+    <t>الصف الأول الثانوي</t>
+  </si>
+  <si>
+    <t>g11</t>
+  </si>
+  <si>
+    <t>grade-11</t>
+  </si>
+  <si>
+    <t>الصف الثاني الثانوي</t>
+  </si>
+  <si>
+    <t>g12</t>
+  </si>
+  <si>
+    <t>grade-12</t>
+  </si>
+  <si>
+    <t>الصف الثالث الثانوي</t>
+  </si>
+  <si>
+    <t>— المسارات المعتمدة —</t>
+  </si>
+  <si>
+    <t>sanaa</t>
+  </si>
+  <si>
+    <t>منهج صنعاء</t>
+  </si>
+  <si>
+    <t>aden</t>
+  </si>
+  <si>
+    <t>منهج عدن</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>آخر</t>
+  </si>
+  <si>
+    <t>sub-g10-aden-001</t>
+  </si>
+  <si>
+    <t>lesson-g10-aden-001-001</t>
+  </si>
+  <si>
+    <t>exp-g10-aden-001-001-01</t>
   </si>
   <si>
     <t>شرح النظام الدولي للوحدات</t>
@@ -511,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -653,6 +807,14 @@
         <v>27</v>
       </c>
     </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -660,6 +822,249 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="52" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -696,25 +1101,25 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/public/content-import-templates/05_lesson_explanations_template.xlsx
+++ b/public/content-import-templates/05_lesson_explanations_template.xlsx
@@ -36,19 +36,19 @@
     <t>subject_code *</t>
   </si>
   <si>
-    <t>ملاحظة: إلزامي — يحدد المادة التي ينتمي إليها lesson_code — مثال: sub-g10-aden-001</t>
+    <t>ملاحظة: إلزامي — يحدد المادة التي ينتمي إليها lesson_code — مثال: sub-g10-001</t>
   </si>
   <si>
     <t>lesson_code *</t>
   </si>
   <si>
-    <t>مثال: lesson-g10-aden-001-001</t>
+    <t>مثال: lesson-g10-001-001</t>
   </si>
   <si>
     <t>explanation_code *</t>
   </si>
   <si>
-    <t>ملاحظة: هوية ثابتة للشرح — لا تغيّرها بين الدفعات — مثال: exp-g10-aden-001-001-01</t>
+    <t>ملاحظة: هوية ثابتة للشرح — لا تغيّرها بين الدفعات — مثال: exp-g10-001-001-01</t>
   </si>
   <si>
     <t>title *</t>
@@ -252,13 +252,13 @@
     <t>آخر</t>
   </si>
   <si>
-    <t>sub-g10-aden-001</t>
-  </si>
-  <si>
-    <t>lesson-g10-aden-001-001</t>
-  </si>
-  <si>
-    <t>exp-g10-aden-001-001-01</t>
+    <t>sub-g10-001</t>
+  </si>
+  <si>
+    <t>lesson-g10-001-001</t>
+  </si>
+  <si>
+    <t>exp-g10-001-001-01</t>
   </si>
   <si>
     <t>شرح النظام الدولي للوحدات</t>
